--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -541,7 +541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1254컬럼 (2026-09-21)</t>
+          <t>BRONZE 노출감사 — 전 원천 1254컬럼 (2026-09-22)</t>
         </is>
       </c>
     </row>
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>542</v>
+        <v>492</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -703,11 +703,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>522</v>
+        <v>472</v>
       </c>
       <c r="H20" t="n">
         <v>58</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
         <v>1064</v>
@@ -11265,19 +11265,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -11713,19 +11713,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -12001,19 +12001,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -13761,19 +13761,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D157" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D157" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -14177,19 +14177,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D170" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D170" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -14753,19 +14753,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D188" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D188" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -15297,19 +15297,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D205" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D205" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E205" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F205" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -15777,19 +15777,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D220" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D220" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E220" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F220" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -16481,19 +16481,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D242" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D242" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E242" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F242" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -17345,19 +17345,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D269" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D269" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E269" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F269" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -17761,19 +17761,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D282" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D282" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E282" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F282" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -18337,19 +18337,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D300" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D300" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E300" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F300" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -19009,19 +19009,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D321" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D321" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E321" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F321" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -19521,19 +19521,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D337" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D337" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E337" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F337" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -19905,19 +19905,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D349" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D349" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E349" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F349" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -20385,19 +20385,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D364" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D364" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E364" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F364" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -20673,19 +20673,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D373" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D373" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E373" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F373" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -22273,19 +22273,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D423" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D423" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E423" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F423" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -22657,19 +22657,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D435" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D435" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E435" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F435" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -23873,19 +23873,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D473" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D473" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E473" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F473" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -24353,19 +24353,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D488" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D488" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E488" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F488" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -24737,19 +24737,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D500" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D500" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E500" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F500" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -25249,19 +25249,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D516" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D516" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E516" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F516" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -25441,19 +25441,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D522" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D522" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E522" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F522" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -26209,19 +26209,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D546" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D546" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E546" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F546" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -27233,19 +27233,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D578" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D578" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E578" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F578" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -27809,19 +27809,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D596" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D596" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E596" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F596" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -28257,19 +28257,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D610" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D610" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E610" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F610" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -28513,19 +28513,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D618" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D618" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E618" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F618" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -28833,19 +28833,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D628" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D628" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E628" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F628" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -29153,19 +29153,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D638" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D638" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E638" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F638" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -29473,19 +29473,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D648" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D648" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E648" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F648" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -30209,19 +30209,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D671" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D671" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E671" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F671" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -31361,19 +31361,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D707" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D707" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E707" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F707" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -31905,19 +31905,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D724" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D724" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E724" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F724" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -32449,19 +32449,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D741" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D741" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E741" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F741" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -32897,19 +32897,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D755" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D755" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E755" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F755" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -33601,19 +33601,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D777" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D777" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E777" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F777" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -34145,19 +34145,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D794" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D794" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E794" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F794" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -35137,19 +35137,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D825" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D825" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E825" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F825" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -35681,19 +35681,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D842" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D842" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E842" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F842" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -37537,19 +37537,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D900" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D900" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E900" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F900" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -38017,19 +38017,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D915" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D915" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E915" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F915" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -39681,19 +39681,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D967" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D967" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E967" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F967" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -40353,19 +40353,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D988" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D988" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E988" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F988" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -40865,19 +40865,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1004" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1004" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E1004" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F1004" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -41185,19 +41185,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1014" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1014" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E1014" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F1014" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -41857,19 +41857,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1035" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1035" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E1035" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F1035" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -42401,19 +42401,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1052" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1052" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E1052" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F1052" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>
@@ -42849,19 +42849,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1066" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1066" s="17" t="inlineStr">
+        <is>
+          <t>제외(적재제어메타)</t>
         </is>
       </c>
       <c r="E1066" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F1066" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>BRONZE 적재 제어 컬럼 — SILVER 미승격 확정(O175)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,6 +155,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,7 +544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1309컬럼 (2026-09-28)</t>
+          <t>BRONZE 노출감사 — 전 원천 1309컬럼 (2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -583,11 +586,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119</v>
+        <v>343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -613,11 +616,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -628,11 +631,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
     </row>
@@ -658,11 +661,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>536</v>
+        <v>325</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
     </row>
@@ -797,7 +800,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
@@ -806,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
@@ -834,22 +837,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>517</v>
+        <v>306</v>
       </c>
       <c r="H20" t="n">
         <v>61</v>
@@ -912,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1118,7 +1121,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1696,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1793,7 +1796,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2434,100 +2437,100 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_ORG.sql</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PAYMENT_SK</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>365</v>
+        <v>52</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0 as PAYMENT_SK</t>
+          <t>CAST(NULL AS VARCHAR) as PATH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.sql, FACT_MEMBER_FEE.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PLATFORM_TYPE</t>
+          <t>PAYMENT_SK</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>39</v>
+        <v>365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PLATFORM_TYPE</t>
+          <t>0 as PAYMENT_SK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_PAYMENT.sql, FACT_MEMBER_FEE.sql</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PREV_MBER_STAT_CD</t>
+          <t>PLATFORM_TYPE</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PREV_MBER_STAT_CD</t>
+          <t>CAST(NULL AS VARCHAR) as PLATFORM_TYPE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>WIDE_MEMBER_EVENT.sql, WIDE_MEMBER_MONTHLY.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.sql</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PROMO_METHOD_NAME_AT_EVENT</t>
+          <t>PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>208</v>
+        <v>63</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as PROMO_METHOD_NAME_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WIDE_MEMBER_EVENT.sql, WIDE_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
@@ -2539,20 +2542,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>REASON_SK</t>
+          <t>PROMO_METHOD_NAME_AT_EVENT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0 as REASON_SK</t>
+          <t>CAST(NULL AS VARCHAR) as PROMO_METHOD_NAME_AT_EVENT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DIM_REASON.sql, FACT_MEMBER_MONTHLY.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2564,40 +2567,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>REGION_AT_EVENT</t>
+          <t>REASON_SK</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as REGION_AT_EVENT</t>
+          <t>0 as REASON_SK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_REASON.sql, FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FACT_EVENT_ATTENDANCE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SELF_PART_FLAG</t>
+          <t>REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CAST(NULL AS BOOLEAN) as SELF_PART_FLAG</t>
+          <t>CAST(NULL AS VARCHAR) as REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2609,20 +2612,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FACT_MESSAGE_DISPATCH.sql</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEND_STATUS2</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
+          <t>CAST(NULL AS VARCHAR) as RM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2634,20 +2637,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_EVENT_ATTENDANCE.sql</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEX_AT_EVENT</t>
+          <t>SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
+          <t>CAST(NULL AS BOOLEAN) as SELF_PART_FLAG</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2659,20 +2662,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_MESSAGE_DISPATCH.sql</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPNSR_AMT</t>
+          <t>SEND_STATUS2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
+          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2684,20 +2687,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SPNSR_DIV_CD_AT_EVENT</t>
+          <t>SETLE_CMPNY_ACNT_ID</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_CD_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as SETLE_CMPNY_ACNT_ID</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2714,15 +2717,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPNSR_DIV_NM_AT_EVENT</t>
+          <t>SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_NM_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2734,175 +2737,175 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>SPNSR_AMT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FACT_BUDGET_YEARLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>53</v>
+        <v>202</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FACT_EVENT_ATTENDANCE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_BUDGET_YEARLY.sql</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL_NM</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_EVENT_ATTENDANCE.sql</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>STOP_CHANNEL</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>425</v>
+        <v>96</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2914,15 +2917,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STOP_REASON</t>
+          <t>STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2939,65 +2942,65 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STOP_REASON_NM</t>
+          <t>STOP_DATE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FACT_TARGET_PROJECT.sql</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SUPP_CUM_GOAL_CNT</t>
+          <t>STOP_DATE</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TARGET_GROUP</t>
+          <t>STOP_REASON</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3009,23 +3012,98 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>FACT_MEMBER_EVENT.sql</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>STOP_REASON_NM</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>97</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.sql</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SUPP_CUM_GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>33</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DIM_AD_CREATIVE.sql</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TARGET_GROUP</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>51</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>DIM_ORG.sql</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>TEAM</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>41</v>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C89" t="n">
+        <v>69</v>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>CAST(NULL AS VARCHAR) as TEAM</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7049,9 +7127,9 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -7061,7 +7139,7 @@
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -7081,9 +7159,9 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -7093,7 +7171,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -7113,9 +7191,9 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -7125,7 +7203,7 @@
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -8967,19 +9045,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -8999,19 +9077,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -9031,19 +9109,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -9287,19 +9365,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -9319,19 +9397,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -9351,19 +9429,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -9703,19 +9781,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -9767,19 +9845,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -10407,19 +10485,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -13479,19 +13557,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D159" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13511,19 +13589,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D160" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13543,19 +13621,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D161" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13575,19 +13653,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D162" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13607,9 +13685,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D163" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
@@ -13619,7 +13697,7 @@
       </c>
       <c r="F163" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -13767,19 +13845,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D168" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D168" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13895,19 +13973,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D172" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D172" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -14023,19 +14101,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D176" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D176" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -14055,9 +14133,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D177" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
@@ -14067,7 +14145,7 @@
       </c>
       <c r="F177" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -14311,19 +14389,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D185" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D185" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -14471,19 +14549,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D190" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -14503,19 +14581,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D191" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -14599,19 +14677,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D194" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -14631,9 +14709,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D195" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D195" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
@@ -14643,7 +14721,7 @@
       </c>
       <c r="F195" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -14887,19 +14965,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D203" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D203" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E203" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F203" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15015,19 +15093,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D207" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D207" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E207" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F207" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15047,19 +15125,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D208" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E208" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F208" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15079,19 +15157,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D209" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D209" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E209" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F209" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15111,19 +15189,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D210" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E210" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F210" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15143,19 +15221,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D211" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D211" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E211" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F211" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15175,19 +15253,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D212" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E212" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F212" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15239,19 +15317,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D214" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D214" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E214" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F214" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15367,19 +15445,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D218" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D218" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E218" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F218" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -15943,9 +16021,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D236" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D236" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E236" s="11" t="inlineStr">
@@ -15955,7 +16033,7 @@
       </c>
       <c r="F236" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -16071,19 +16149,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D240" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E240" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F240" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -16935,19 +17013,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D267" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D267" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E267" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F267" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -17351,19 +17429,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D280" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D280" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E280" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F280" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -17767,9 +17845,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D293" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D293" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E293" s="11" t="inlineStr">
@@ -17779,7 +17857,7 @@
       </c>
       <c r="F293" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -17927,19 +18005,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D298" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D298" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E298" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F298" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -18599,19 +18677,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D319" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D319" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E319" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F319" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -18983,19 +19061,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D331" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D331" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E331" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F331" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19079,19 +19157,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D334" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D334" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E334" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F334" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19495,19 +19573,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D347" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D347" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E347" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F347" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19751,19 +19829,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D355" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D355" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E355" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F355" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19975,19 +20053,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D362" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D362" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E362" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F362" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20135,19 +20213,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D367" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D367" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E367" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F367" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20167,19 +20245,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D368" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D368" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E368" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F368" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20391,19 +20469,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D375" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D375" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E375" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F375" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20423,19 +20501,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D376" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D376" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E376" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F376" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20487,19 +20565,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D378" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D378" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E378" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F378" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -20615,19 +20693,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D382" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D382" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E382" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F382" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20647,19 +20725,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D383" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D383" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E383" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F383" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20679,19 +20757,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D384" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D384" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E384" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F384" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20711,19 +20789,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D385" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D385" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E385" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F385" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20743,19 +20821,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D386" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D386" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E386" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F386" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20775,19 +20853,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D387" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D387" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E387" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F387" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -20807,19 +20885,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D388" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D388" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E388" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F388" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20839,19 +20917,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D389" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D389" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E389" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F389" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -20871,19 +20949,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D390" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D390" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E390" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F390" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20903,19 +20981,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D391" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D391" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E391" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F391" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -20935,19 +21013,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D392" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D392" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E392" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F392" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20967,19 +21045,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D393" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D393" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E393" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F393" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -20999,19 +21077,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D394" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D394" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E394" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F394" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21031,19 +21109,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D395" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D395" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E395" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F395" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -21063,19 +21141,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D396" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D396" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E396" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F396" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -21095,19 +21173,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D397" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D397" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E397" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F397" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21127,19 +21205,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D398" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D398" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E398" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F398" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21159,19 +21237,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D399" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D399" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E399" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F399" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -21191,19 +21269,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D400" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D400" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E400" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F400" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21223,19 +21301,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D401" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D401" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E401" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F401" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21255,19 +21333,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D402" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D402" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E402" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F402" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21287,19 +21365,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D403" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D403" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E403" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F403" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21319,19 +21397,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D404" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D404" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E404" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F404" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21351,19 +21429,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D405" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D405" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E405" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F405" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21383,19 +21461,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D406" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D406" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E406" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F406" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21415,19 +21493,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D407" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D407" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E407" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F407" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21447,19 +21525,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D408" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D408" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E408" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F408" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21479,19 +21557,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D409" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D409" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E409" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F409" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21511,19 +21589,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D410" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D410" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E410" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F410" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21543,19 +21621,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D411" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D411" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E411" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F411" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -21575,19 +21653,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D412" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D412" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E412" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F412" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -21607,19 +21685,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D413" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D413" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E413" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F413" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21639,19 +21717,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D414" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D414" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E414" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F414" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21671,19 +21749,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D415" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D415" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E415" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F415" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21703,19 +21781,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D416" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D416" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E416" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F416" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21735,19 +21813,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D417" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D417" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E417" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F417" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -21831,19 +21909,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D420" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D420" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E420" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F420" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -21863,19 +21941,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D421" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D421" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E421" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F421" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -22247,19 +22325,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D433" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D433" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E433" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F433" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -23175,19 +23253,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D462" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D462" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E462" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F462" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -23207,9 +23285,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D463" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D463" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E463" s="11" t="inlineStr">
@@ -23219,7 +23297,7 @@
       </c>
       <c r="F463" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -23687,19 +23765,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D478" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D478" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E478" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F478" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -23911,19 +23989,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D485" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D485" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E485" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F485" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -24327,19 +24405,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D498" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D498" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E498" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F498" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -24487,19 +24565,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D503" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D503" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E503" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F503" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24551,19 +24629,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D505" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D505" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E505" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F505" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24583,19 +24661,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D506" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D506" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E506" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F506" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24615,19 +24693,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D507" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D507" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E507" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F507" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24647,19 +24725,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D508" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D508" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E508" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F508" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24679,19 +24757,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D509" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D509" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E509" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F509" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -24711,19 +24789,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D510" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D510" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E510" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F510" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24743,19 +24821,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D511" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D511" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E511" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F511" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24775,19 +24853,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D512" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D512" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E512" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F512" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24807,19 +24885,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D513" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D513" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E513" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F513" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24839,19 +24917,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D514" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D514" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E514" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F514" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24871,19 +24949,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D515" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D515" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E515" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F515" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24903,19 +24981,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D516" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D516" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E516" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F516" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24935,19 +25013,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D517" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D517" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E517" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F517" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24967,19 +25045,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D518" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D518" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E518" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F518" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -24999,19 +25077,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D519" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D519" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E519" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F519" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -25031,19 +25109,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D520" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D520" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E520" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F520" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -25063,19 +25141,19 @@
           <t>FLOAT</t>
         </is>
       </c>
-      <c r="D521" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D521" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E521" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F521" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -25127,19 +25205,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D523" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D523" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E523" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>낮음(토큰만)</t>
         </is>
       </c>
       <c r="F523" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD SQL 토큰 출현 — 적재 미확인</t>
         </is>
       </c>
     </row>
@@ -25159,19 +25237,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D524" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D524" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E524" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>낮음(토큰만)</t>
         </is>
       </c>
       <c r="F524" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD SQL 토큰 출현 — 적재 미확인</t>
         </is>
       </c>
     </row>
@@ -25223,19 +25301,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D526" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D526" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E526" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>낮음(토큰만)</t>
         </is>
       </c>
       <c r="F526" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD SQL 토큰 출현 — 적재 미확인</t>
         </is>
       </c>
     </row>
@@ -25351,19 +25429,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D530" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D530" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E530" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F530" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -25639,19 +25717,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D539" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D539" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E539" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F539" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -25703,9 +25781,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D541" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D541" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E541" s="11" t="inlineStr">
@@ -25715,7 +25793,7 @@
       </c>
       <c r="F541" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -25863,19 +25941,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D546" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D546" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E546" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F546" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -26247,19 +26325,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D558" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D558" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E558" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F558" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -26279,19 +26357,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D559" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D559" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E559" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F559" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -27175,19 +27253,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D587" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D587" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E587" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F587" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -27975,19 +28053,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D612" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D612" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E612" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F612" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28007,19 +28085,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D613" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D613" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E613" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F613" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28551,19 +28629,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D630" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D630" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E630" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F630" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28583,19 +28661,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D631" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D631" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E631" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F631" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28743,19 +28821,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D636" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D636" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E636" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F636" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28775,19 +28853,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D637" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D637" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E637" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F637" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28807,19 +28885,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D638" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D638" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E638" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F638" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28839,19 +28917,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D639" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D639" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E639" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F639" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -28871,19 +28949,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D640" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D640" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E640" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F640" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -29031,19 +29109,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D645" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D645" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E645" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F645" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -29959,19 +30037,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D674" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D674" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E674" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F674" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -30951,19 +31029,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D705" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D705" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E705" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F705" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31015,19 +31093,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D707" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D707" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E707" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F707" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31047,19 +31125,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D708" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D708" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E708" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F708" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31079,19 +31157,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D709" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D709" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E709" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F709" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31111,19 +31189,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D710" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D710" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E710" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F710" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31143,19 +31221,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D711" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D711" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E711" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F711" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31175,19 +31253,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D712" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D712" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E712" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F712" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31207,19 +31285,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D713" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D713" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E713" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F713" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -31239,19 +31317,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D714" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D714" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E714" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F714" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31271,19 +31349,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D715" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D715" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E715" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F715" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31303,19 +31381,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D716" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D716" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E716" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F716" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31335,19 +31413,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D717" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D717" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E717" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F717" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -31367,19 +31445,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D718" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D718" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E718" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F718" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31399,19 +31477,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D719" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D719" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E719" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F719" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31431,19 +31509,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D720" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D720" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E720" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F720" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31463,19 +31541,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D721" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D721" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E721" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F721" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31495,19 +31573,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D722" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D722" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E722" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F722" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -31623,19 +31701,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D726" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D726" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E726" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F726" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -32295,9 +32373,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D747" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D747" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E747" s="11" t="inlineStr">
@@ -32307,7 +32385,7 @@
       </c>
       <c r="F747" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -32423,19 +32501,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D751" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D751" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E751" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F751" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -32647,19 +32725,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D758" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D758" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E758" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F758" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -32967,19 +33045,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D768" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D768" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E768" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F768" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -32999,19 +33077,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D769" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D769" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E769" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F769" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33095,19 +33173,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D772" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D772" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E772" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F772" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33351,19 +33429,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D780" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D780" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E780" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F780" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33479,19 +33557,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D784" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D784" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E784" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F784" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -33543,19 +33621,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D786" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D786" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E786" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F786" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33575,19 +33653,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D787" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D787" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E787" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F787" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33607,19 +33685,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D788" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D788" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E788" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F788" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33639,19 +33717,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D789" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D789" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E789" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F789" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33671,19 +33749,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D790" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D790" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E790" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F790" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -33703,19 +33781,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D791" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D791" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E791" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F791" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33735,19 +33813,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D792" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D792" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E792" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F792" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33767,19 +33845,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D793" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D793" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E793" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F793" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33895,19 +33973,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D797" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D797" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E797" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F797" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34343,19 +34421,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D811" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D811" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E811" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F811" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34503,19 +34581,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D816" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D816" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E816" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F816" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34535,19 +34613,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D817" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D817" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E817" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F817" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34695,19 +34773,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D822" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D822" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E822" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F822" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34855,19 +34933,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D827" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D827" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E827" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F827" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34887,19 +34965,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D828" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D828" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E828" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F828" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34919,19 +34997,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D829" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D829" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E829" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F829" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35047,19 +35125,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D833" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D833" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E833" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F833" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35207,19 +35285,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D838" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D838" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E838" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F838" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35239,19 +35317,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D839" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D839" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E839" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F839" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35591,19 +35669,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D850" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D850" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E850" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F850" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35911,19 +35989,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D860" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D860" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E860" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F860" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35943,19 +36021,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D861" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D861" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E861" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F861" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -36007,19 +36085,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D863" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D863" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E863" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F863" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -36039,19 +36117,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D864" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D864" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E864" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F864" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -36071,19 +36149,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D865" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D865" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E865" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F865" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -36423,9 +36501,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D876" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D876" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E876" s="11" t="inlineStr">
@@ -36435,7 +36513,7 @@
       </c>
       <c r="F876" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -36551,19 +36629,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D880" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D880" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E880" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F880" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -36711,19 +36789,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D885" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D885" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E885" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F885" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -36775,19 +36853,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D887" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D887" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E887" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F887" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -36807,19 +36885,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D888" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D888" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E888" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F888" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -36839,19 +36917,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D889" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D889" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E889" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F889" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -36871,19 +36949,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D890" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D890" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E890" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F890" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -36903,19 +36981,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D891" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D891" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E891" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F891" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -36935,19 +37013,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D892" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D892" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E892" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F892" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -36967,19 +37045,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D893" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D893" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E893" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F893" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37127,19 +37205,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D898" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D898" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E898" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F898" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37479,19 +37557,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D909" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D909" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E909" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F909" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37863,19 +37941,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D921" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D921" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E921" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F921" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37927,19 +38005,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D923" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D923" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E923" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F923" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37959,19 +38037,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D924" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D924" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E924" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F924" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -38311,19 +38389,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D935" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D935" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E935" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F935" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -38375,19 +38453,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D937" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D937" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E937" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F937" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -38407,19 +38485,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D938" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D938" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E938" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F938" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -38439,19 +38517,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D939" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D939" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E939" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F939" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -38759,9 +38837,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D949" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D949" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E949" s="11" t="inlineStr">
@@ -38771,7 +38849,7 @@
       </c>
       <c r="F949" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -38919,19 +38997,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D954" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D954" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E954" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F954" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39111,19 +39189,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D960" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D960" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E960" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F960" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -39143,19 +39221,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D961" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D961" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E961" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F961" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -39175,19 +39253,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D962" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D962" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E962" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F962" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:17 `CAST(NULL AS VARCHAR) as SETLE_CMPNY_ACNT_ID`</t>
         </is>
       </c>
     </row>
@@ -39239,19 +39317,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D964" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D964" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E964" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="F964" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 미승격</t>
         </is>
       </c>
     </row>
@@ -39271,19 +39349,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D965" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D965" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E965" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F965" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39303,9 +39381,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D966" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D966" s="18" t="inlineStr">
+        <is>
+          <t>⚠️설계O·값미주입</t>
         </is>
       </c>
       <c r="E966" s="11" t="inlineStr">
@@ -39315,7 +39393,7 @@
       </c>
       <c r="F966" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql:19 `CAST(NULL AS VARCHAR) as RM`</t>
         </is>
       </c>
     </row>
@@ -39463,19 +39541,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D971" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D971" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E971" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F971" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39591,19 +39669,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D975" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D975" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E975" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F975" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39719,19 +39797,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D979" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D979" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E979" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F979" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39751,19 +39829,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D980" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D980" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E980" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F980" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39815,19 +39893,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D982" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D982" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E982" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F982" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39847,19 +39925,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D983" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D983" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E983" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F983" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39879,19 +39957,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D984" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D984" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E984" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F984" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39911,19 +39989,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D985" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D985" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E985" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F985" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -39943,19 +40021,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D986" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D986" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E986" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F986" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -39975,19 +40053,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D987" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D987" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E987" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F987" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40007,19 +40085,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D988" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D988" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E988" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F988" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40071,19 +40149,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D990" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D990" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E990" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F990" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40103,19 +40181,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D991" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D991" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E991" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F991" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40135,19 +40213,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D992" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D992" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E992" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F992" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40167,19 +40245,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D993" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D993" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E993" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F993" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40199,19 +40277,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D994" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D994" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E994" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F994" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40231,19 +40309,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D995" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D995" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E995" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F995" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40263,19 +40341,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D996" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D996" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E996" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F996" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40295,19 +40373,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D997" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D997" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E997" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F997" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40327,19 +40405,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D998" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D998" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E998" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F998" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40359,19 +40437,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D999" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D999" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E999" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F999" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40391,19 +40469,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1000" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1000" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1000" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1000" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40423,19 +40501,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1001" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1001" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1001" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1001" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40455,19 +40533,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1002" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1002" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1002" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1002" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40487,19 +40565,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1003" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1003" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1003" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1003" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40519,19 +40597,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1004" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1004" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1004" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1004" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40551,19 +40629,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1005" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1005" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1005" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1005" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40583,19 +40661,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1006" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1006" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1006" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1006" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40615,19 +40693,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1007" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1007" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1007" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1007" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40647,19 +40725,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1008" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1008" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1008" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1008" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40679,19 +40757,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1009" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1009" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E1009" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F1009" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40743,19 +40821,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1011" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1011" s="14" t="inlineStr">
+        <is>
+          <t>SILVER까지만</t>
         </is>
       </c>
       <c r="E1011" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(SQL참조)</t>
         </is>
       </c>
       <c r="F1011" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>SILVER SQL 토큰 참조</t>
         </is>
       </c>
     </row>
@@ -40775,19 +40853,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1012" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1012" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1012" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1012" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40807,19 +40885,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1013" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1013" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1013" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1013" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40839,19 +40917,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1014" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1014" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1014" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1014" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40871,19 +40949,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1015" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1015" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1015" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1015" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -40903,19 +40981,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1016" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1016" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1016" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1016" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41127,19 +41205,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D1023" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1023" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1023" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1023" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41255,19 +41333,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1027" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1027" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1027" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1027" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41287,19 +41365,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1028" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1028" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1028" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1028" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41319,19 +41397,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1029" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1029" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1029" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1029" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41351,19 +41429,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1030" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1030" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1030" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1030" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41383,19 +41461,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1031" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1031" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1031" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1031" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41415,19 +41493,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1032" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1032" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1032" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1032" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41447,19 +41525,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1033" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1033" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1033" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1033" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41479,19 +41557,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1034" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1034" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1034" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1034" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41511,19 +41589,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1035" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1035" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1035" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1035" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41543,19 +41621,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1036" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1036" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1036" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1036" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41575,19 +41653,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1037" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1037" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1037" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1037" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41607,19 +41685,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1038" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1038" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1038" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1038" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41639,19 +41717,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1039" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1039" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1039" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1039" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41671,19 +41749,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1040" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1040" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1040" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1040" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41799,19 +41877,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D1044" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1044" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1044" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1044" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41927,19 +42005,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1048" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1048" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1048" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1048" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41959,19 +42037,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1049" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1049" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1049" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1049" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -41991,19 +42069,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1050" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1050" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1050" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1050" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42055,19 +42133,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1052" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1052" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1052" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1052" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42087,19 +42165,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1053" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1053" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1053" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1053" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42119,19 +42197,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1054" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1054" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1054" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1054" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42151,19 +42229,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1055" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1055" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1055" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1055" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42215,19 +42293,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D1057" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1057" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1057" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1057" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42247,19 +42325,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D1058" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1058" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1058" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1058" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42279,19 +42357,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1059" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1059" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1059" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1059" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42311,19 +42389,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1060" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1060" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1060" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1060" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42439,19 +42517,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1064" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1064" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1064" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1064" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42471,19 +42549,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1065" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1065" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1065" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1065" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42503,19 +42581,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1066" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1066" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1066" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1066" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42535,19 +42613,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1067" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1067" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1067" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1067" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42567,19 +42645,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1068" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1068" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1068" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1068" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42599,19 +42677,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1069" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1069" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1069" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1069" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42631,19 +42709,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1070" s="16" t="inlineStr">
-        <is>
-          <t>미노출(검토대상)</t>
+      <c r="D1070" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1070" s="11" t="inlineStr">
         <is>
-          <t>낮음(이름기반·P13)</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1070" s="11" t="inlineStr">
         <is>
-          <t>개명·VARIANT param 승격 가능성 — 확정 아님</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42759,19 +42837,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1074" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1074" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1074" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1074" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43431,19 +43509,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1095" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1095" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1095" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1095" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43975,19 +44053,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1112" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1112" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1112" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1112" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -44071,19 +44149,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1115" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1115" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1115" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1115" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -544,7 +544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1310컬럼 (2026-10-01)</t>
+          <t>BRONZE 노출감사 — 전 원천 1310컬럼 (2026-10-02)</t>
         </is>
       </c>
     </row>
@@ -586,11 +586,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>379</v>
+        <v>440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
     </row>
@@ -631,11 +631,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>471</v>
+        <v>410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>31.3%</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>370</v>
+        <v>309</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8572,19 +8572,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -9180,19 +9180,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -11068,19 +11068,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -11516,19 +11516,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D96" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -11932,19 +11932,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -12060,19 +12060,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -12156,19 +12156,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D116" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13020,19 +13020,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D143" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13052,9 +13052,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D144" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -13084,9 +13084,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D145" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -13116,9 +13116,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D146" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -13180,19 +13180,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D148" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -13404,19 +13404,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D155" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -16252,19 +16252,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D244" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D244" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E244" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F244" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -16444,19 +16444,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D250" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D250" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E250" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F250" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -16476,19 +16476,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D251" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D251" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E251" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F251" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -16508,19 +16508,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D252" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D252" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E252" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F252" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -17116,19 +17116,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D271" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D271" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E271" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F271" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -17180,19 +17180,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D273" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D273" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E273" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F273" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -18108,19 +18108,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D302" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D302" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E302" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F302" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -18300,19 +18300,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D308" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D308" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E308" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F308" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -18780,19 +18780,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D323" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D323" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E323" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F323" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19292,19 +19292,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D339" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D339" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E339" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F339" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19356,19 +19356,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D341" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D341" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E341" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F341" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19388,19 +19388,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D342" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D342" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E342" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F342" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19676,19 +19676,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D351" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D351" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E351" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F351" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -19740,19 +19740,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D353" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D353" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E353" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F353" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="F563" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `ORG_SK` (FACT_MEMBER_EVENT.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_MEMBER_EVENT.sql:148 `0 as ORG_SK`</t>
+          <t>개명 적재 → GOLD `ORG_SK` (FACT_MEMBER_EVENT.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_MEMBER_EVENT.sql:157 `0 as ORG_SK`</t>
         </is>
       </c>
     </row>
@@ -33020,19 +33020,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D768" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D768" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E768" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F768" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33116,19 +33116,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D771" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D771" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E771" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F771" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33148,19 +33148,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D772" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D772" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E772" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F772" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33244,19 +33244,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D775" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D775" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E775" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F775" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -33308,19 +33308,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D777" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D777" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E777" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F777" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34556,19 +34556,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D816" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D816" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E816" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F816" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34652,19 +34652,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D819" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D819" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E819" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F819" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34684,19 +34684,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D820" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D820" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E820" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F820" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -34844,19 +34844,19 @@
           <t>TIMESTAMP_NTZ</t>
         </is>
       </c>
-      <c r="D825" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D825" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E825" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F825" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35260,19 +35260,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D838" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D838" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E838" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F838" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35356,19 +35356,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D841" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D841" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E841" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F841" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35388,19 +35388,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D842" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D842" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E842" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F842" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35420,19 +35420,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D843" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D843" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E843" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F843" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35516,19 +35516,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D846" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D846" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E846" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F846" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -35548,19 +35548,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D847" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D847" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E847" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F847" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37340,19 +37340,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D903" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D903" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E903" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F903" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -37788,19 +37788,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D917" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D917" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E917" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F917" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42908,19 +42908,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1077" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1077" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1077" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1077" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -42940,19 +42940,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1078" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1078" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1078" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1078" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43036,19 +43036,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1081" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1081" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1081" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1081" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43068,19 +43068,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1082" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1082" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1082" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1082" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43164,19 +43164,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1085" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1085" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1085" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1085" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43228,19 +43228,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1087" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1087" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1087" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1087" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43260,19 +43260,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1088" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1088" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1088" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1088" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43292,19 +43292,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1089" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1089" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1089" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1089" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43356,19 +43356,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1091" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1091" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1091" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1091" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43580,19 +43580,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1098" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1098" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1098" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1098" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43644,19 +43644,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1100" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1100" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1100" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1100" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43676,19 +43676,19 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="D1101" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1101" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1101" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1101" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43708,19 +43708,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1102" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1102" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1102" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1102" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43836,19 +43836,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1106" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1106" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1106" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1106" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43868,19 +43868,19 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D1107" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1107" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1107" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1107" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43900,19 +43900,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1108" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1108" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1108" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1108" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>
@@ -43932,19 +43932,19 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="D1109" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D1109" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E1109" s="11" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간(스키마만)</t>
         </is>
       </c>
       <c r="F1109" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>GOLD 컬럼 존재하나 dbt projection 미확인 — 값 유무 실측 필요(P15)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -544,7 +544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1310컬럼 (2026-10-02)</t>
+          <t>BRONZE 노출감사 — 전 원천 1310컬럼 (2026-10-07)</t>
         </is>
       </c>
     </row>
@@ -586,11 +586,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
     </row>
@@ -631,11 +631,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>2</v>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>215</v>
+        <v>289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>199</v>
+        <v>273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>200</v>
+        <v>274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>202</v>
+        <v>276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>214</v>
+        <v>288</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>193</v>
+        <v>267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>195</v>
+        <v>269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>204</v>
+        <v>278</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>207</v>
+        <v>281</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2637,20 +2637,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FACT_MESSAGE_DISPATCH.sql</t>
+          <t>DIM_PAYMENT_ACCOUNT.sql</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEND_STATUS2</t>
+          <t>SETLE_CMPNY_ACNT_ID</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEND_STATUS2</t>
+          <t>CAST(NULL AS VARCHAR) as SETLE_CMPNY_ACNT_ID</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2662,20 +2662,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT_ACCOUNT.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SETLE_CMPNY_ACNT_ID</t>
+          <t>SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
+        <v>266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SETLE_CMPNY_ACNT_ID</t>
+          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2692,15 +2692,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEX_AT_EVENT</t>
+          <t>SPNSR_AMT</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SEX_AT_EVENT</t>
+          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2717,15 +2717,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPNSR_AMT</t>
+          <t>SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>164</v>
+        <v>285</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,0)) as SPNSR_AMT</t>
+          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2742,15 +2742,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SPNSR_DIV_CD_AT_EVENT</t>
+          <t>SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_CD_AT_EVENT</t>
+          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2762,32 +2762,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_BUDGET.sql</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPNSR_DIV_NM_AT_EVENT</t>
+          <t>SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>212</v>
+        <v>45</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as SPNSR_DIV_NM_AT_EVENT</t>
+          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.sql</t>
+          <t>FACT_BUDGET_YEARLY.sql</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FACT_BUDGET_YEARLY.sql</t>
+          <t>FACT_EVENT_ATTENDANCE.sql</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2821,11 +2821,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(38,0)) as SPONSORSHIP_SK</t>
+          <t>0 as SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2837,25 +2837,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FACT_EVENT_ATTENDANCE.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_SK</t>
+          <t>STOP_CHANNEL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0 as SPONSORSHIP_SK</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.sql, FACT_MEMBER_EVENT.sql, FACT_MEMBER_FEE.sql, FACT_MEMBER_MONTHLY.sql, FACT_MEMBER_SPONSORSHIP_SPAN.sql, FACT_TARGET_PROJECT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2867,15 +2867,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL</t>
+          <t>STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2892,70 +2892,70 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL_NM</t>
+          <t>STOP_DATE</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_CHANNEL_NM</t>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>FACT_MEMBER_MONTHLY.sql</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>STOP_DATE</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>430</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>FACT_MEMBER_EVENT.sql</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>STOP_DATE</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>103</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_MONTHLY.sql</t>
+          <t>FACT_MEMBER_EVENT.sql</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>STOP_REASON</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>425</v>
+        <v>170</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CAST(NULL AS DATE) as STOP_DATE</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2967,15 +2967,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STOP_REASON</t>
+          <t>STOP_REASON_NM</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON</t>
+          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2987,20 +2987,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.sql</t>
+          <t>FACT_TARGET_PROJECT.sql</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STOP_REASON_NM</t>
+          <t>SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as STOP_REASON_NM</t>
+          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3012,20 +3012,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FACT_TARGET_PROJECT.sql</t>
+          <t>DIM_AD_CREATIVE.sql</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SUPP_CUM_GOAL_CNT</t>
+          <t>TARGET_GROUP</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CAST(NULL AS NUMBER(18,4)) as SUPP_CUM_GOAL_CNT</t>
+          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3037,48 +3037,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DIM_AD_CREATIVE.sql</t>
+          <t>DIM_ORG.sql</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TARGET_GROUP</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CAST(NULL AS VARCHAR) as TARGET_GROUP</t>
+          <t>CAST(NULL AS VARCHAR) as TEAM</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>DIM_ORG.sql</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>88</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>CAST(NULL AS VARCHAR) as TEAM</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -24793,7 +24768,7 @@
       </c>
       <c r="C511" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D511" s="14" t="inlineStr">
@@ -24825,7 +24800,7 @@
       </c>
       <c r="C512" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D512" s="14" t="inlineStr">
@@ -24857,7 +24832,7 @@
       </c>
       <c r="C513" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D513" s="14" t="inlineStr">
@@ -24889,7 +24864,7 @@
       </c>
       <c r="C514" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D514" s="14" t="inlineStr">
@@ -24921,7 +24896,7 @@
       </c>
       <c r="C515" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D515" s="14" t="inlineStr">
@@ -24953,7 +24928,7 @@
       </c>
       <c r="C516" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D516" s="14" t="inlineStr">
@@ -24985,7 +24960,7 @@
       </c>
       <c r="C517" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D517" s="14" t="inlineStr">
@@ -25017,7 +24992,7 @@
       </c>
       <c r="C518" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D518" s="14" t="inlineStr">
@@ -25049,7 +25024,7 @@
       </c>
       <c r="C519" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D519" s="14" t="inlineStr">
@@ -25081,7 +25056,7 @@
       </c>
       <c r="C520" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D520" s="14" t="inlineStr">
@@ -25113,7 +25088,7 @@
       </c>
       <c r="C521" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D521" s="14" t="inlineStr">
@@ -25145,7 +25120,7 @@
       </c>
       <c r="C522" s="11" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="D522" s="14" t="inlineStr">
@@ -26472,7 +26447,7 @@
       </c>
       <c r="F563" s="11" t="inlineStr">
         <is>
-          <t>개명 적재 → GOLD `ORG_SK` (FACT_MEMBER_EVENT.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_MEMBER_EVENT.sql:157 `0 as ORG_SK`</t>
+          <t>개명 적재 → GOLD `ORG_SK` (FACT_MEMBER_EVENT.sql) · ⚠️ 일부 브랜치는 센티넬 — FACT_MEMBER_EVENT.sql:231 `0 as ORG_SK`</t>
         </is>
       </c>
     </row>
@@ -44666,9 +44641,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -44678,7 +44653,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -44986,9 +44961,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -44998,7 +44973,7 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>
@@ -46970,9 +46945,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>SILVER까지만</t>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>노출됨(GOLD)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -46982,7 +46957,7 @@
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GOLD 미승격</t>
+          <t>동명 GOLD 컬럼 + 실적재 projection 확인</t>
         </is>
       </c>
     </row>

--- a/30_output_share/06_BRONZE노출감사.xlsx
+++ b/30_output_share/06_BRONZE노출감사.xlsx
@@ -544,7 +544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1314컬럼 (2026-10-25)</t>
+          <t>BRONZE 노출감사 — 전 원천 1314컬럼 (2026-10-27)</t>
         </is>
       </c>
     </row>
